--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/testes_estacionariedade.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/testes_estacionariedade.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IPCA_Geral_nivel</t>
+          <t>Preco_Barril</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6833822923742333</v>
+        <v>-1.990599612592153</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9895003329603416</v>
+        <v>0.2907099913053095</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H2" t="n">
-        <v>1.910116389167523</v>
+        <v>0.9387316912636929</v>
       </c>
       <c r="I2" t="n">
         <v>0.01</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IPCA_Geral_nivel</t>
+          <t>Preco_Barril</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-6.385927952029274</v>
+        <v>-9.120500128579524</v>
       </c>
       <c r="E3" t="n">
-        <v>2.164371603814304e-08</v>
+        <v>3.214956451863754e-15</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1558261052452888</v>
+        <v>0.04112539460402964</v>
       </c>
       <c r="I3" t="n">
         <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>129</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IPCA_Trans_nivel</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3615797428846359</v>
+        <v>-1.660916742723721</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9163186605704752</v>
+        <v>0.4513534265089791</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
         <v>127</v>
       </c>
       <c r="H4" t="n">
-        <v>1.863606220023845</v>
+        <v>1.649114109042418</v>
       </c>
       <c r="I4" t="n">
         <v>0.01</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IPCA_Trans_nivel</t>
+          <t>Cambio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-6.779133539821636</v>
+        <v>-8.658124754900678</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5256670941097e-09</v>
+        <v>4.905368534635617e-14</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -625,13 +625,13 @@
         <v>128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06120539342848424</v>
+        <v>0.1474531303909669</v>
       </c>
       <c r="I5" t="n">
         <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>129</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.660916742723721</v>
+        <v>-1.070450594012347</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4513534265089791</v>
+        <v>0.7267108980353464</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H14" t="n">
-        <v>1.649114109042418</v>
+        <v>1.273815000914052</v>
       </c>
       <c r="I14" t="n">
         <v>0.01</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cambio</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1023,19 +1023,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-8.658124754900678</v>
+        <v>-8.508550568848378</v>
       </c>
       <c r="E15" t="n">
-        <v>4.905368534635617e-14</v>
+        <v>1.184538377757526e-13</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1474531303909669</v>
+        <v>0.1834848744416176</v>
       </c>
       <c r="I15" t="n">
         <v>0.1</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Preco_Barril</t>
+          <t>Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.990599612592153</v>
+        <v>-2.509590288806516</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2907099913053095</v>
+        <v>0.1131583072889067</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9387316912636929</v>
+        <v>0.4034433435949789</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01</v>
+        <v>0.07567097258837116</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Preco_Barril</t>
+          <t>Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-9.120500128579524</v>
+        <v>-9.168592782066026</v>
       </c>
       <c r="E17" t="n">
-        <v>3.214956451863754e-15</v>
+        <v>2.422616133476916e-15</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1117,13 +1117,13 @@
         <v>127</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04112539460402964</v>
+        <v>0.1246740945949461</v>
       </c>
       <c r="I17" t="n">
         <v>0.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
         <v>129</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Selic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1146,22 +1146,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.070450594012347</v>
+        <v>-1.787181108962888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7267108980353464</v>
+        <v>0.3868442320734603</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="H18" t="n">
-        <v>1.273815000914052</v>
+        <v>0.3808055754325889</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01</v>
+        <v>0.08542863127905653</v>
       </c>
       <c r="J18" t="n">
         <v>6</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Selic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-8.508550568848378</v>
+        <v>-3.346099240937537</v>
       </c>
       <c r="E19" t="n">
-        <v>1.184538377757526e-13</v>
+        <v>0.01293945881435194</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1834848744416176</v>
+        <v>0.2811429230190558</v>
       </c>
       <c r="I19" t="n">
         <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>129</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selic</t>
+          <t>IPCA_Trans_nivel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.787181108962888</v>
+        <v>-0.3615797428846359</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3868442320734603</v>
+        <v>0.9163186605704752</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3808055754325889</v>
+        <v>1.863606220023845</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08542863127905653</v>
+        <v>0.01</v>
       </c>
       <c r="J20" t="n">
         <v>6</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selic</t>
+          <t>IPCA_Trans_nivel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3.346099240937537</v>
+        <v>-6.779133539821636</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01293945881435194</v>
+        <v>2.5256670941097e-09</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2811429230190558</v>
+        <v>0.06120539342848424</v>
       </c>
       <c r="I21" t="n">
         <v>0.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>129</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Expectativa_Inflacao</t>
+          <t>IPCA_Geral_nivel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1310,22 +1310,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.509590288806516</v>
+        <v>0.6833822923742333</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1131583072889067</v>
+        <v>0.9895003329603416</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4034433435949789</v>
+        <v>1.910116389167523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07567097258837116</v>
+        <v>0.01</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expectativa_Inflacao</t>
+          <t>IPCA_Geral_nivel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-9.168592782066026</v>
+        <v>-6.385927952029274</v>
       </c>
       <c r="E23" t="n">
-        <v>2.422616133476916e-15</v>
+        <v>2.164371603814304e-08</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1246740945949461</v>
+        <v>0.1558261052452888</v>
       </c>
       <c r="I23" t="n">
         <v>0.1</v>
